--- a/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,13 +562,13 @@
         <v>0.9001831501831502</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9076086956521739</v>
+        <v>0.9092391304347827</v>
       </c>
       <c r="E6" t="n">
         <v>0.7228464419475655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8436444204305709</v>
+        <v>0.844052029126223</v>
       </c>
     </row>
     <row r="7">
@@ -578,26 +579,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[85  3]
- [ 5 10]]</t>
+          <t>[[85, 3], [5, 10]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[82  2]
- [ 7  6]]</t>
+          <t>[[82, 2], [7, 6]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[86  6]
- [ 8 12]]</t>
+          <t>[[86, 6], [8, 12]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[86  3]
- [ 9  3]]</t>
+          <t>[[86, 3], [9, 3]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8737864077669902</v>
+        <v>0.8446601941747572</v>
       </c>
       <c r="C8" t="n">
-        <v>0.845360824742268</v>
+        <v>0.8144329896907216</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7920792079207921</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8286994672503698</v>
+        <v>0.8255759833779679</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8155303030303029</v>
+        <v>0.7984848484848485</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7806776556776557</v>
+        <v>0.7303113553113554</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8021739130434783</v>
+        <v>0.7739130434782608</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7017790262172285</v>
+        <v>0.7186329588014981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7750402244921664</v>
+        <v>0.7553355515189907</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7762740183792816</v>
+        <v>0.7418546365914787</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7261434217955958</v>
+        <v>0.6790441176470587</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7315904139433551</v>
+        <v>0.7348484848484849</v>
       </c>
       <c r="E10" t="n">
-        <v>0.637125748502994</v>
+        <v>0.6658088235294117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7177834006553065</v>
+        <v>0.7053890156541085</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8809564363984395</v>
+        <v>0.8573131858773148</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8584002281895604</v>
+        <v>0.8316252274105518</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8209461562402739</v>
+        <v>0.8322510822510824</v>
       </c>
       <c r="E11" t="n">
-        <v>0.817904784490425</v>
+        <v>0.8398660454280722</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8445519013296747</v>
+        <v>0.8402638852417552</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8848484848484848</v>
       </c>
       <c r="C12" t="n">
-        <v>0.815018315018315</v>
+        <v>0.8534798534798536</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8559782608695652</v>
+        <v>0.8451086956521739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7415730337078652</v>
+        <v>0.75749063670412</v>
       </c>
       <c r="F12" t="n">
-        <v>0.819809069065603</v>
+        <v>0.835231917671158</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[79  9]
- [ 4 11]]</t>
+          <t>[[76, 12], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[73 11]
- [ 4  9]]</t>
+          <t>[[71, 13], [5, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[74 18]
- [ 4 16]]</t>
+          <t>[[78, 14], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[73 16]
- [ 5  7]]</t>
+          <t>[[76, 13], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[75, 14], [4, 11]]</t>
+          <t>[[75, 13], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -765,13 +758,13 @@
         <v>0.865979381443299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8125</v>
       </c>
       <c r="E14" t="n">
         <v>0.8811881188118812</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8650599055769712</v>
+        <v>0.8583634770055426</v>
       </c>
     </row>
     <row r="15">
@@ -787,13 +780,13 @@
         <v>0.5325091575091575</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.533695652173913</v>
       </c>
       <c r="E15" t="n">
         <v>0.5360486891385767</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5817186777357148</v>
+        <v>0.5629686777357148</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +802,13 @@
         <v>0.5303538175046555</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.5272361809045226</v>
       </c>
       <c r="E16" t="n">
         <v>0.5395136778115501</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5960981838013654</v>
+        <v>0.5697439637213735</v>
       </c>
     </row>
     <row r="17">
@@ -831,13 +824,13 @@
         <v>0.8209564399393345</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8097667638483965</v>
+        <v>0.7633165829145729</v>
       </c>
       <c r="E17" t="n">
         <v>0.8419151945589695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8324080777668116</v>
+        <v>0.8207955325333557</v>
       </c>
     </row>
     <row r="18">
@@ -853,13 +846,13 @@
         <v>0.6565934065934066</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6894021739130435</v>
+        <v>0.6739130434782608</v>
       </c>
       <c r="E18" t="n">
         <v>0.6905430711610488</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6871649659471778</v>
+        <v>0.6832926833384821</v>
       </c>
     </row>
     <row r="19">
@@ -870,31 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[85  3]
- [10  5]]</t>
+          <t>[[85, 3], [10, 5]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[83  1]
- [12  1]]</t>
+          <t>[[83, 1], [12, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89  3]
- [15  5]]</t>
+          <t>[[89, 3], [18, 2]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[88  1]
- [11  1]]</t>
+          <t>[[88, 1], [11, 1]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [12, 3]]</t>
+          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
     </row>
@@ -1016,26 +1005,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[68 20]
- [ 5 10]]</t>
+          <t>[[68, 20], [5, 10]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[39 45]
- [ 7  6]]</t>
+          <t>[[39, 45], [7, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[66 26]
- [10 10]]</t>
+          <t>[[66, 26], [10, 10]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[70 19]
- [ 9  3]]</t>
+          <t>[[70, 19], [9, 3]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9029126213592233</v>
+        <v>0.912621359223301</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8969072164948454</v>
+        <v>0.9072164948453608</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="E26" t="n">
         <v>0.9108910891089109</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8897313031693163</v>
+        <v>0.8925036643658217</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7496212121212121</v>
+        <v>0.7553030303030304</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6141304347826086</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="E27" t="n">
         <v>0.625</v>
       </c>
       <c r="F27" t="n">
-        <v>0.651034065572109</v>
+        <v>0.6607112090807743</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7799145299145299</v>
+        <v>0.7951381215469613</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6594101123595506</v>
+        <v>0.7098703888334995</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6420379770633577</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="E28" t="n">
         <v>0.6759358288770054</v>
       </c>
       <c r="F28" t="n">
-        <v>0.689324612053611</v>
+        <v>0.7033993501204889</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8965231101153431</v>
+        <v>0.9050903824491765</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8675865863546854</v>
+        <v>0.8850150579190263</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8166814385088497</v>
+        <v>0.8097667638483965</v>
       </c>
       <c r="E29" t="n">
         <v>0.886302747921851</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8667734707251824</v>
+        <v>0.8715437380346127</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9098484848484849</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8434065934065934</v>
+        <v>0.8360805860805861</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8201086956521739</v>
+        <v>0.7956521739130434</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7921348314606741</v>
+        <v>0.7659176029962547</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8413746513419815</v>
+        <v>0.8266853180201983</v>
       </c>
     </row>
     <row r="31">
@@ -1162,29 +1147,411 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[85  3]
- [ 7  8]]</t>
+          <t>[[86, 2], [7, 8]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[84  0]
- [10  3]]</t>
+          <t>[[84, 0], [9, 4]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[90  2]
- [15  5]]</t>
+          <t>[[89, 3], [15, 5]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[89  0]
- [ 9  3]]</t>
+          <t>[[89, 0], [9, 3]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
+        <is>
+          <t>[[87, 1], [10, 5]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8964336776861551</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01922708563612713</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7276724298539761</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.07712719733551661</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7516466770369236</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07329346447307403</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8883025048742784</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.02217245375808186</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.844052029126223</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07431498499314974</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[85, 4], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>413</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8255759833779679</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01140139677321872</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7553355515189907</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.03232752598084525</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7053890156541085</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03338505314954636</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8402638852417552</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01036422150442317</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.835231917671158</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04726533721825828</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[75, 13], [5, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>413</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8583634770055426</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.02701986116869885</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5629686777357148</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05004507942713698</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5697439637213735</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.06489434103132623</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8207955325333557</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03556760602263093</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6832926833384821</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02052121596039025</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[86, 2], [13, 2]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>413</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6556356962426013</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.114150235970885</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5773907841873158</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09725360245944226</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5286657507205781</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.09223925723795152</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6989045677793586</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.09316556951154288</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6544035547378855</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08578333864861211</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[61, 28], [8, 7]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8925036643658217</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03078732136168182</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6607112090807743</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05695535584969015</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7033993501204889</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05961786417784366</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8715437380346127</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03654133523614525</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8266853180201983</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05369991555870086</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>[[87, 1], [10, 5]]</t>
         </is>

--- a/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8737864077669902</v>
+        <v>0.8640776699029126</v>
       </c>
       <c r="C14" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8125</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E14" t="n">
         <v>0.8811881188118812</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8583634770055426</v>
+        <v>0.860745754984295</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6496212121212122</v>
+        <v>0.6162878787878788</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5325091575091575</v>
+        <v>0.5709706959706959</v>
       </c>
       <c r="D15" t="n">
-        <v>0.533695652173913</v>
+        <v>0.558695652173913</v>
       </c>
       <c r="E15" t="n">
         <v>0.5360486891385767</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5629686777357148</v>
+        <v>0.5705007290177662</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.681872178664766</v>
+        <v>0.6437747035573123</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5303538175046555</v>
+        <v>0.5912921348314606</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5272361809045226</v>
+        <v>0.5648795648795649</v>
       </c>
       <c r="E16" t="n">
         <v>0.5395136778115501</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5697439637213735</v>
+        <v>0.5848650202699719</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8569939127205457</v>
+        <v>0.8423193522391496</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8209564399393345</v>
+        <v>0.8411039036256226</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7633165829145729</v>
+        <v>0.7796647796647797</v>
       </c>
       <c r="E17" t="n">
         <v>0.8419151945589695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8207955325333557</v>
+        <v>0.8262508075221303</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7121212121212122</v>
+        <v>0.6981060606060607</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6565934065934066</v>
+        <v>0.6524725274725276</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6739130434782608</v>
+        <v>0.6942934782608696</v>
       </c>
       <c r="E18" t="n">
         <v>0.6905430711610488</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6832926833384821</v>
+        <v>0.6838537843751268</v>
       </c>
     </row>
     <row r="19">
@@ -863,17 +863,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[85, 3], [10, 5]]</t>
+          <t>[[85, 3], [11, 4]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[83, 1], [12, 1]]</t>
+          <t>[[83, 1], [11, 2]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89, 3], [18, 2]]</t>
+          <t>[[89, 3], [17, 3]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [13, 2]]</t>
+          <t>[[86, 2], [12, 2]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8583634770055426</v>
+        <v>0.860745754984295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02701986116869885</v>
+        <v>0.02353940689862722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5629686777357148</v>
+        <v>0.5705007290177662</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05004507942713698</v>
+        <v>0.02925314873707663</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5697439637213735</v>
+        <v>0.5848650202699719</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06489434103132623</v>
+        <v>0.03862583745546575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8207955325333557</v>
+        <v>0.8262508075221303</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03556760602263093</v>
+        <v>0.02690001675625952</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6832926833384821</v>
+        <v>0.6838537843751268</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02052121596039025</v>
+        <v>0.01831423236640087</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 2], [13, 2]]</t>
+          <t>[[86, 2], [12, 2]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,16 +613,16 @@
         <v>0.8446601941747572</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8144329896907216</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="D8" t="n">
         <v>0.8214285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.8415841584158416</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8255759833779679</v>
+        <v>0.8382584371903595</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.7984848484848485</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7303113553113554</v>
+        <v>0.7481684981684982</v>
       </c>
       <c r="D9" t="n">
         <v>0.7739130434782608</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7186329588014981</v>
+        <v>0.7298689138576779</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7553355515189907</v>
+        <v>0.7626088259973214</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.7418546365914787</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6790441176470587</v>
+        <v>0.712052246190382</v>
       </c>
       <c r="D10" t="n">
         <v>0.7348484848484849</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6658088235294117</v>
+        <v>0.6868217054263566</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7053890156541085</v>
+        <v>0.7188942682641755</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.8573131858773148</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8316252274105518</v>
+        <v>0.8554599594810471</v>
       </c>
       <c r="D11" t="n">
         <v>0.8322510822510824</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8398660454280722</v>
+        <v>0.8546626755698824</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8402638852417552</v>
+        <v>0.8499217257948317</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.8848484848484848</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8534798534798536</v>
+        <v>0.7976190476190476</v>
       </c>
       <c r="D12" t="n">
         <v>0.8451086956521739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.75749063670412</v>
+        <v>0.7865168539325843</v>
       </c>
       <c r="F12" t="n">
-        <v>0.835231917671158</v>
+        <v>0.8285232705130726</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[71, 13], [5, 8]]</t>
+          <t>[[74, 10], [5, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[76, 13], [5, 7]]</t>
+          <t>[[78, 11], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[75, 13], [5, 10]]</t>
+          <t>[[76, 12], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8255759833779679</v>
+        <v>0.8382584371903595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01140139677321872</v>
+        <v>0.009820020425821677</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7553355515189907</v>
+        <v>0.7626088259973214</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03232752598084525</v>
+        <v>0.02595813570490658</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7053890156541085</v>
+        <v>0.7188942682641755</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03338505314954636</v>
+        <v>0.02154749459675416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8402638852417552</v>
+        <v>0.8499217257948317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01036422150442317</v>
+        <v>0.01024736505807561</v>
       </c>
       <c r="N3" t="n">
-        <v>0.835231917671158</v>
+        <v>0.8285232705130726</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04726533721825828</v>
+        <v>0.03926581249506993</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[75, 13], [5, 10]]</t>
+          <t>[[76, 12], [5, 10]]</t>
         </is>
       </c>
     </row>
